--- a/pregenerated_results/att_evalue_survey.xlsx
+++ b/pregenerated_results/att_evalue_survey.xlsx
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4993210257416965</v>
+        <v>0.4911400218600746</v>
       </c>
       <c r="D2" t="n">
-        <v>1.575199818981437</v>
+        <v>1.563516451197447</v>
       </c>
       <c r="E2" t="n">
-        <v>2.527068849225469</v>
+        <v>2.502168272677388</v>
       </c>
       <c r="F2" t="n">
-        <v>2.071911862906451</v>
+        <v>2.256833721249756</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,11 +510,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-value = 2.53. An unmeasured confounder would need risk ratio associations of at least 2.53 with both treatment and outcome to explain away this effect. This represents moderate robustness. The E-value for the confidence interval bound is 2.07, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 2.50. An unmeasured confounder would need risk ratio associations of at least 2.50 with both treatment and outcome to explain away this effect. This represents moderate robustness. The E-value for the confidence interval bound is 2.26, meaning a confounder of this strength could shift the CI to include the null. For continuous outcomes, E-value uses an approximate RR conversion; interpretation is approximate.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.216315028059068e-31</v>
+        <v>3.590526857595078e-31</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.04256676218162209</v>
+        <v>-0.04668816531796489</v>
       </c>
       <c r="D3" t="n">
-        <v>1.039495764326114</v>
+        <v>1.04340168909192</v>
       </c>
       <c r="E3" t="n">
-        <v>1.242117776274022</v>
+        <v>1.256205344389361</v>
       </c>
       <c r="F3" t="n">
-        <v>1.480806964352357</v>
+        <v>1.503037354997255</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,11 +550,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-value = 1.24. This effect is highly sensitive to unmeasured confounding and could easily be explained by a weak confounder. The E-value for the confidence interval bound is 1.48, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 1.26. This effect is highly sensitive to unmeasured confounding and could easily be explained by a weak confounder. The E-value for the confidence interval bound is 1.50, meaning a confounder of this strength could shift the CI to include the null. For continuous outcomes, E-value uses an approximate RR conversion; interpretation is approximate.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.2414710814149321</v>
+        <v>0.2419674343520269</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.295112936491181</v>
+        <v>0.2724759382114328</v>
       </c>
       <c r="D4" t="n">
-        <v>1.308070004950221</v>
+        <v>1.281399837966493</v>
       </c>
       <c r="E4" t="n">
-        <v>1.942874804002851</v>
+        <v>1.881887728580502</v>
       </c>
       <c r="F4" t="n">
-        <v>1.64630190867069</v>
+        <v>1.675495925656325</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -590,11 +590,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-value = 1.94. A relatively weak unmeasured confounder (RR ≈ 1.94) could potentially explain this effect. Interpret with caution. The E-value for the confidence interval bound is 1.65, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 1.88. A relatively weak unmeasured confounder (RR ≈ 1.88) could potentially explain this effect. Interpret with caution. The E-value for the confidence interval bound is 1.68, meaning a confounder of this strength could shift the CI to include the null. For continuous outcomes, E-value uses an approximate RR conversion; interpretation is approximate.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9.590676754544794e-12</v>
+        <v>8.430217045679813e-12</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
